--- a/artfynd/A 50503-2023 artfynd.xlsx
+++ b/artfynd/A 50503-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50503-2023 artfynd.xlsx
+++ b/artfynd/A 50503-2023 artfynd.xlsx
@@ -9063,10 +9063,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119625593</v>
+        <v>119625398</v>
       </c>
       <c r="B77" t="n">
-        <v>91826</v>
+        <v>78171</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9079,21 +9079,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3100</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9103,10 +9103,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>545146</v>
+        <v>544657</v>
       </c>
       <c r="R77" t="n">
-        <v>6961121</v>
+        <v>6961420</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9165,10 +9165,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119625390</v>
+        <v>119625593</v>
       </c>
       <c r="B78" t="n">
-        <v>91852</v>
+        <v>91826</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9177,25 +9177,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4366</v>
+        <v>3100</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9205,10 +9205,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>544640</v>
+        <v>545146</v>
       </c>
       <c r="R78" t="n">
-        <v>6961471</v>
+        <v>6961121</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9267,10 +9267,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119625398</v>
+        <v>119625390</v>
       </c>
       <c r="B79" t="n">
-        <v>78171</v>
+        <v>91852</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9279,25 +9279,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9307,10 +9307,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>544657</v>
+        <v>544640</v>
       </c>
       <c r="R79" t="n">
-        <v>6961420</v>
+        <v>6961471</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9573,10 +9573,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119625592</v>
+        <v>119625393</v>
       </c>
       <c r="B82" t="n">
-        <v>91832</v>
+        <v>89633</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9589,21 +9589,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4361</v>
+        <v>1962</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9613,10 +9613,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>545146</v>
+        <v>544660</v>
       </c>
       <c r="R82" t="n">
-        <v>6961121</v>
+        <v>6961435</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9675,10 +9675,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119625384</v>
+        <v>119625592</v>
       </c>
       <c r="B83" t="n">
-        <v>91858</v>
+        <v>91832</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9691,21 +9691,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4368</v>
+        <v>4361</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9715,10 +9715,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>544582</v>
+        <v>545146</v>
       </c>
       <c r="R83" t="n">
-        <v>6961543</v>
+        <v>6961121</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9777,10 +9777,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119625393</v>
+        <v>119625384</v>
       </c>
       <c r="B84" t="n">
-        <v>89633</v>
+        <v>91858</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9793,21 +9793,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1962</v>
+        <v>4368</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>544660</v>
+        <v>544582</v>
       </c>
       <c r="R84" t="n">
-        <v>6961435</v>
+        <v>6961543</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>

--- a/artfynd/A 50503-2023 artfynd.xlsx
+++ b/artfynd/A 50503-2023 artfynd.xlsx
@@ -9063,10 +9063,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119625398</v>
+        <v>119625593</v>
       </c>
       <c r="B77" t="n">
-        <v>78171</v>
+        <v>91826</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9079,21 +9079,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>353</v>
+        <v>3100</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9103,10 +9103,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>544657</v>
+        <v>545146</v>
       </c>
       <c r="R77" t="n">
-        <v>6961420</v>
+        <v>6961121</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9165,10 +9165,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119625593</v>
+        <v>119625390</v>
       </c>
       <c r="B78" t="n">
-        <v>91826</v>
+        <v>91852</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9177,25 +9177,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3100</v>
+        <v>4366</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9205,10 +9205,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>545146</v>
+        <v>544640</v>
       </c>
       <c r="R78" t="n">
-        <v>6961121</v>
+        <v>6961471</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9267,10 +9267,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119625390</v>
+        <v>119625398</v>
       </c>
       <c r="B79" t="n">
-        <v>91852</v>
+        <v>78171</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9279,25 +9279,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9307,10 +9307,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>544640</v>
+        <v>544657</v>
       </c>
       <c r="R79" t="n">
-        <v>6961471</v>
+        <v>6961420</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>

--- a/artfynd/A 50503-2023 artfynd.xlsx
+++ b/artfynd/A 50503-2023 artfynd.xlsx
@@ -5283,10 +5283,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119625584</v>
+        <v>119625393</v>
       </c>
       <c r="B40" t="n">
-        <v>89230</v>
+        <v>89633</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5295,25 +5295,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1596</v>
+        <v>1962</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5323,10 +5323,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>545189</v>
+        <v>544660</v>
       </c>
       <c r="R40" t="n">
-        <v>6961120</v>
+        <v>6961435</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5385,10 +5385,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119625386</v>
+        <v>119625383</v>
       </c>
       <c r="B41" t="n">
-        <v>91856</v>
+        <v>91852</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5397,25 +5397,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5425,10 +5425,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544563</v>
+        <v>544594</v>
       </c>
       <c r="R41" t="n">
-        <v>6961544</v>
+        <v>6961545</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5487,10 +5487,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119625373</v>
+        <v>119625599</v>
       </c>
       <c r="B42" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5503,21 +5503,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544694</v>
+        <v>545111</v>
       </c>
       <c r="R42" t="n">
-        <v>6961492</v>
+        <v>6961107</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5589,10 +5589,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119625583</v>
+        <v>119625612</v>
       </c>
       <c r="B43" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5605,21 +5605,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5629,10 +5629,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>545192</v>
+        <v>544836</v>
       </c>
       <c r="R43" t="n">
-        <v>6961119</v>
+        <v>6961292</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5691,7 +5691,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119625395</v>
+        <v>119625615</v>
       </c>
       <c r="B44" t="n">
         <v>91840</v>
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544660</v>
+        <v>544748</v>
       </c>
       <c r="R44" t="n">
-        <v>6961435</v>
+        <v>6961477</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5793,10 +5793,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119625387</v>
+        <v>119625398</v>
       </c>
       <c r="B45" t="n">
-        <v>77910</v>
+        <v>78171</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5809,21 +5809,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5833,10 +5833,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>544571</v>
+        <v>544657</v>
       </c>
       <c r="R45" t="n">
-        <v>6961517</v>
+        <v>6961420</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5895,7 +5895,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119625576</v>
+        <v>119625579</v>
       </c>
       <c r="B46" t="n">
         <v>91834</v>
@@ -5935,10 +5935,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>545048</v>
+        <v>545270</v>
       </c>
       <c r="R46" t="n">
-        <v>6960895</v>
+        <v>6960997</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5997,10 +5997,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119625377</v>
+        <v>119625591</v>
       </c>
       <c r="B47" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6013,21 +6013,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6037,10 +6037,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544634</v>
+        <v>545162</v>
       </c>
       <c r="R47" t="n">
-        <v>6961537</v>
+        <v>6961129</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6081,6 +6081,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6099,10 +6100,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119625598</v>
+        <v>119625384</v>
       </c>
       <c r="B48" t="n">
-        <v>91834</v>
+        <v>91858</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6115,21 +6116,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4362</v>
+        <v>4368</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6139,10 +6140,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>545110</v>
+        <v>544582</v>
       </c>
       <c r="R48" t="n">
-        <v>6961114</v>
+        <v>6961543</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6201,10 +6202,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119625578</v>
+        <v>119625386</v>
       </c>
       <c r="B49" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6217,21 +6218,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6241,10 +6242,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>545085</v>
+        <v>544563</v>
       </c>
       <c r="R49" t="n">
-        <v>6960933</v>
+        <v>6961544</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6303,10 +6304,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119625597</v>
+        <v>119625381</v>
       </c>
       <c r="B50" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6315,25 +6316,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6343,10 +6344,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>545109</v>
+        <v>544635</v>
       </c>
       <c r="R50" t="n">
-        <v>6961124</v>
+        <v>6961580</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6405,10 +6406,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119625606</v>
+        <v>119625592</v>
       </c>
       <c r="B51" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6417,25 +6418,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6445,10 +6446,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>544967</v>
+        <v>545146</v>
       </c>
       <c r="R51" t="n">
-        <v>6961196</v>
+        <v>6961121</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6489,7 +6490,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6508,7 +6508,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119625594</v>
+        <v>119625385</v>
       </c>
       <c r="B52" t="n">
         <v>91834</v>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>545146</v>
+        <v>544570</v>
       </c>
       <c r="R52" t="n">
-        <v>6961121</v>
+        <v>6961546</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6610,10 +6610,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119625579</v>
+        <v>119625373</v>
       </c>
       <c r="B53" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6626,21 +6626,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6650,10 +6650,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>545270</v>
+        <v>544694</v>
       </c>
       <c r="R53" t="n">
-        <v>6960997</v>
+        <v>6961492</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6712,7 +6712,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119625585</v>
+        <v>119625574</v>
       </c>
       <c r="B54" t="n">
         <v>91834</v>
@@ -6752,10 +6752,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>545189</v>
+        <v>544964</v>
       </c>
       <c r="R54" t="n">
-        <v>6961131</v>
+        <v>6960939</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6814,10 +6814,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119625607</v>
+        <v>119625392</v>
       </c>
       <c r="B55" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6826,25 +6826,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6854,10 +6854,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>544911</v>
+        <v>544655</v>
       </c>
       <c r="R55" t="n">
-        <v>6961201</v>
+        <v>6961452</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6916,10 +6916,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119625374</v>
+        <v>119625597</v>
       </c>
       <c r="B56" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6928,25 +6928,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6956,10 +6956,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>544655</v>
+        <v>545109</v>
       </c>
       <c r="R56" t="n">
-        <v>6961490</v>
+        <v>6961124</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7018,7 +7018,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119625574</v>
+        <v>119625582</v>
       </c>
       <c r="B57" t="n">
         <v>91834</v>
@@ -7058,10 +7058,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>544964</v>
+        <v>545184</v>
       </c>
       <c r="R57" t="n">
-        <v>6960939</v>
+        <v>6961041</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7120,10 +7120,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119625601</v>
+        <v>119625576</v>
       </c>
       <c r="B58" t="n">
-        <v>56522</v>
+        <v>91834</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7132,42 +7132,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>4362</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>545027</v>
+        <v>545048</v>
       </c>
       <c r="R58" t="n">
-        <v>6961112</v>
+        <v>6960895</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7226,10 +7222,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119625382</v>
+        <v>119625603</v>
       </c>
       <c r="B59" t="n">
-        <v>90807</v>
+        <v>91884</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7238,25 +7234,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>65</v>
+        <v>5449</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7266,10 +7262,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>544614</v>
+        <v>544968</v>
       </c>
       <c r="R59" t="n">
-        <v>6961561</v>
+        <v>6961151</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7328,10 +7324,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119625383</v>
+        <v>119625598</v>
       </c>
       <c r="B60" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7340,25 +7336,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7368,10 +7364,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>544594</v>
+        <v>545110</v>
       </c>
       <c r="R60" t="n">
-        <v>6961545</v>
+        <v>6961114</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7532,10 +7528,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119625381</v>
+        <v>119625585</v>
       </c>
       <c r="B62" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7544,25 +7540,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7572,10 +7568,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>544635</v>
+        <v>545189</v>
       </c>
       <c r="R62" t="n">
-        <v>6961580</v>
+        <v>6961131</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7634,10 +7630,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119625599</v>
+        <v>119625607</v>
       </c>
       <c r="B63" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7646,25 +7642,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7674,10 +7670,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>545111</v>
+        <v>544911</v>
       </c>
       <c r="R63" t="n">
-        <v>6961107</v>
+        <v>6961201</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7838,10 +7834,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119625385</v>
+        <v>119625387</v>
       </c>
       <c r="B65" t="n">
-        <v>91834</v>
+        <v>77910</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7854,21 +7850,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4362</v>
+        <v>6437</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7878,10 +7874,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>544570</v>
+        <v>544571</v>
       </c>
       <c r="R65" t="n">
-        <v>6961546</v>
+        <v>6961517</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7940,10 +7936,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119625596</v>
+        <v>119625584</v>
       </c>
       <c r="B66" t="n">
-        <v>91834</v>
+        <v>89230</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7952,25 +7948,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4362</v>
+        <v>1596</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7980,10 +7976,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>545102</v>
+        <v>545189</v>
       </c>
       <c r="R66" t="n">
-        <v>6961133</v>
+        <v>6961120</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8042,10 +8038,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119625580</v>
+        <v>119625391</v>
       </c>
       <c r="B67" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8054,25 +8050,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8082,10 +8078,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>545279</v>
+        <v>544660</v>
       </c>
       <c r="R67" t="n">
-        <v>6961027</v>
+        <v>6961476</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8144,7 +8140,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119625591</v>
+        <v>119625580</v>
       </c>
       <c r="B68" t="n">
         <v>91834</v>
@@ -8184,10 +8180,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>545162</v>
+        <v>545279</v>
       </c>
       <c r="R68" t="n">
-        <v>6961129</v>
+        <v>6961027</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8228,7 +8224,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8247,10 +8242,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119625388</v>
+        <v>119625380</v>
       </c>
       <c r="B69" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8263,21 +8258,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8287,10 +8282,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>544609</v>
+        <v>544678</v>
       </c>
       <c r="R69" t="n">
-        <v>6961486</v>
+        <v>6961634</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8349,10 +8344,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119625575</v>
+        <v>119625583</v>
       </c>
       <c r="B70" t="n">
-        <v>89252</v>
+        <v>91856</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8361,25 +8356,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8389,10 +8384,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>545016</v>
+        <v>545192</v>
       </c>
       <c r="R70" t="n">
-        <v>6960898</v>
+        <v>6961119</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8451,10 +8446,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119625603</v>
+        <v>119625388</v>
       </c>
       <c r="B71" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8467,21 +8462,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8491,10 +8486,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>544968</v>
+        <v>544609</v>
       </c>
       <c r="R71" t="n">
-        <v>6961151</v>
+        <v>6961486</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8553,10 +8548,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119625612</v>
+        <v>119625596</v>
       </c>
       <c r="B72" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8569,21 +8564,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8593,10 +8588,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>544836</v>
+        <v>545102</v>
       </c>
       <c r="R72" t="n">
-        <v>6961292</v>
+        <v>6961133</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8655,10 +8650,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119625582</v>
+        <v>119625377</v>
       </c>
       <c r="B73" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8671,21 +8666,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8695,10 +8690,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>545184</v>
+        <v>544634</v>
       </c>
       <c r="R73" t="n">
-        <v>6961041</v>
+        <v>6961537</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8757,10 +8752,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119625392</v>
+        <v>119625395</v>
       </c>
       <c r="B74" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8769,25 +8764,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8797,10 +8792,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>544655</v>
+        <v>544660</v>
       </c>
       <c r="R74" t="n">
-        <v>6961452</v>
+        <v>6961435</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8859,10 +8854,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119625615</v>
+        <v>119625593</v>
       </c>
       <c r="B75" t="n">
-        <v>91840</v>
+        <v>91826</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8871,25 +8866,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8899,10 +8894,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>544748</v>
+        <v>545146</v>
       </c>
       <c r="R75" t="n">
-        <v>6961477</v>
+        <v>6961121</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8961,10 +8956,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119625391</v>
+        <v>119625601</v>
       </c>
       <c r="B76" t="n">
-        <v>91840</v>
+        <v>56522</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8977,34 +8972,38 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>544660</v>
+        <v>545027</v>
       </c>
       <c r="R76" t="n">
-        <v>6961476</v>
+        <v>6961112</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9063,10 +9062,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119625593</v>
+        <v>119625594</v>
       </c>
       <c r="B77" t="n">
-        <v>91826</v>
+        <v>91834</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9079,21 +9078,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9165,10 +9164,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119625390</v>
+        <v>119625578</v>
       </c>
       <c r="B78" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9177,25 +9176,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9205,10 +9204,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>544640</v>
+        <v>545085</v>
       </c>
       <c r="R78" t="n">
-        <v>6961471</v>
+        <v>6960933</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9267,10 +9266,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119625398</v>
+        <v>119625581</v>
       </c>
       <c r="B79" t="n">
-        <v>78171</v>
+        <v>91832</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9283,21 +9282,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9307,10 +9306,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>544657</v>
+        <v>545208</v>
       </c>
       <c r="R79" t="n">
-        <v>6961420</v>
+        <v>6961020</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9369,10 +9368,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119625380</v>
+        <v>119625382</v>
       </c>
       <c r="B80" t="n">
-        <v>91856</v>
+        <v>90807</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9381,25 +9380,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2059</v>
+        <v>65</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9409,10 +9408,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>544678</v>
+        <v>544614</v>
       </c>
       <c r="R80" t="n">
-        <v>6961634</v>
+        <v>6961561</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9471,10 +9470,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119625581</v>
+        <v>119625606</v>
       </c>
       <c r="B81" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9483,25 +9482,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9511,10 +9510,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>545208</v>
+        <v>544967</v>
       </c>
       <c r="R81" t="n">
-        <v>6961020</v>
+        <v>6961196</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9555,6 +9554,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9573,10 +9573,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119625393</v>
+        <v>119625575</v>
       </c>
       <c r="B82" t="n">
-        <v>89633</v>
+        <v>89252</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9585,25 +9585,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1962</v>
+        <v>6276</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9613,10 +9613,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>544660</v>
+        <v>545016</v>
       </c>
       <c r="R82" t="n">
-        <v>6961435</v>
+        <v>6960898</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9675,10 +9675,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119625592</v>
+        <v>119625390</v>
       </c>
       <c r="B83" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9687,25 +9687,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9715,10 +9715,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>545146</v>
+        <v>544640</v>
       </c>
       <c r="R83" t="n">
-        <v>6961121</v>
+        <v>6961471</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9777,10 +9777,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119625384</v>
+        <v>119625374</v>
       </c>
       <c r="B84" t="n">
-        <v>91858</v>
+        <v>91840</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9789,25 +9789,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4368</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>544582</v>
+        <v>544655</v>
       </c>
       <c r="R84" t="n">
-        <v>6961543</v>
+        <v>6961490</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>

--- a/artfynd/A 50503-2023 artfynd.xlsx
+++ b/artfynd/A 50503-2023 artfynd.xlsx
@@ -5283,10 +5283,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119625393</v>
+        <v>119625383</v>
       </c>
       <c r="B40" t="n">
-        <v>89633</v>
+        <v>91852</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5295,25 +5295,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1962</v>
+        <v>4366</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5323,10 +5323,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544660</v>
+        <v>544594</v>
       </c>
       <c r="R40" t="n">
-        <v>6961435</v>
+        <v>6961545</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5385,10 +5385,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119625383</v>
+        <v>119625612</v>
       </c>
       <c r="B41" t="n">
-        <v>91852</v>
+        <v>91884</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5397,25 +5397,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5425,10 +5425,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544594</v>
+        <v>544836</v>
       </c>
       <c r="R41" t="n">
-        <v>6961545</v>
+        <v>6961292</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5487,10 +5487,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119625599</v>
+        <v>119625393</v>
       </c>
       <c r="B42" t="n">
-        <v>91834</v>
+        <v>89633</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5503,21 +5503,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>545111</v>
+        <v>544660</v>
       </c>
       <c r="R42" t="n">
-        <v>6961107</v>
+        <v>6961435</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5589,10 +5589,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119625612</v>
+        <v>119625599</v>
       </c>
       <c r="B43" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5605,21 +5605,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5629,10 +5629,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544836</v>
+        <v>545111</v>
       </c>
       <c r="R43" t="n">
-        <v>6961292</v>
+        <v>6961107</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -6304,10 +6304,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119625381</v>
+        <v>119625592</v>
       </c>
       <c r="B50" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6316,25 +6316,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>544635</v>
+        <v>545146</v>
       </c>
       <c r="R50" t="n">
-        <v>6961580</v>
+        <v>6961121</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6406,10 +6406,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119625592</v>
+        <v>119625385</v>
       </c>
       <c r="B51" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6422,21 +6422,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>545146</v>
+        <v>544570</v>
       </c>
       <c r="R51" t="n">
-        <v>6961121</v>
+        <v>6961546</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6508,10 +6508,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119625385</v>
+        <v>119625373</v>
       </c>
       <c r="B52" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6524,21 +6524,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>544570</v>
+        <v>544694</v>
       </c>
       <c r="R52" t="n">
-        <v>6961546</v>
+        <v>6961492</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6610,10 +6610,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119625373</v>
+        <v>119625381</v>
       </c>
       <c r="B53" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6622,25 +6622,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6650,10 +6650,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>544694</v>
+        <v>544635</v>
       </c>
       <c r="R53" t="n">
-        <v>6961492</v>
+        <v>6961580</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -7222,10 +7222,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119625603</v>
+        <v>119625598</v>
       </c>
       <c r="B59" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7238,21 +7238,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7262,10 +7262,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>544968</v>
+        <v>545110</v>
       </c>
       <c r="R59" t="n">
-        <v>6961151</v>
+        <v>6961114</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7324,7 +7324,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119625598</v>
+        <v>119625396</v>
       </c>
       <c r="B60" t="n">
         <v>91834</v>
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>545110</v>
+        <v>544660</v>
       </c>
       <c r="R60" t="n">
-        <v>6961114</v>
+        <v>6961435</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7426,7 +7426,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119625396</v>
+        <v>119625585</v>
       </c>
       <c r="B61" t="n">
         <v>91834</v>
@@ -7466,10 +7466,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>544660</v>
+        <v>545189</v>
       </c>
       <c r="R61" t="n">
-        <v>6961435</v>
+        <v>6961131</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7528,10 +7528,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119625585</v>
+        <v>119625603</v>
       </c>
       <c r="B62" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7544,21 +7544,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7568,10 +7568,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>545189</v>
+        <v>544968</v>
       </c>
       <c r="R62" t="n">
-        <v>6961131</v>
+        <v>6961151</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -8548,10 +8548,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119625596</v>
+        <v>119625601</v>
       </c>
       <c r="B72" t="n">
-        <v>91834</v>
+        <v>56522</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8560,38 +8560,42 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4362</v>
+        <v>100138</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>545102</v>
+        <v>545027</v>
       </c>
       <c r="R72" t="n">
-        <v>6961133</v>
+        <v>6961112</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8650,10 +8654,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119625377</v>
+        <v>119625596</v>
       </c>
       <c r="B73" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8666,21 +8670,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8690,10 +8694,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>544634</v>
+        <v>545102</v>
       </c>
       <c r="R73" t="n">
-        <v>6961537</v>
+        <v>6961133</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8752,10 +8756,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119625395</v>
+        <v>119625593</v>
       </c>
       <c r="B74" t="n">
-        <v>91840</v>
+        <v>91826</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8764,25 +8768,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8792,10 +8796,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>544660</v>
+        <v>545146</v>
       </c>
       <c r="R74" t="n">
-        <v>6961435</v>
+        <v>6961121</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8854,10 +8858,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119625593</v>
+        <v>119625395</v>
       </c>
       <c r="B75" t="n">
-        <v>91826</v>
+        <v>91840</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8866,25 +8870,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8894,10 +8898,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>545146</v>
+        <v>544660</v>
       </c>
       <c r="R75" t="n">
-        <v>6961121</v>
+        <v>6961435</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8956,10 +8960,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119625601</v>
+        <v>119625377</v>
       </c>
       <c r="B76" t="n">
-        <v>56522</v>
+        <v>91832</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8968,42 +8972,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100138</v>
+        <v>4361</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>545027</v>
+        <v>544634</v>
       </c>
       <c r="R76" t="n">
-        <v>6961112</v>
+        <v>6961537</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9675,10 +9675,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119625390</v>
+        <v>119625374</v>
       </c>
       <c r="B83" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9691,21 +9691,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9715,10 +9715,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>544640</v>
+        <v>544655</v>
       </c>
       <c r="R83" t="n">
-        <v>6961471</v>
+        <v>6961490</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9777,10 +9777,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119625374</v>
+        <v>119625390</v>
       </c>
       <c r="B84" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9793,21 +9793,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>544655</v>
+        <v>544640</v>
       </c>
       <c r="R84" t="n">
-        <v>6961490</v>
+        <v>6961471</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>

--- a/artfynd/A 50503-2023 artfynd.xlsx
+++ b/artfynd/A 50503-2023 artfynd.xlsx
@@ -5283,10 +5283,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119625383</v>
+        <v>119625393</v>
       </c>
       <c r="B40" t="n">
-        <v>91852</v>
+        <v>89633</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5295,25 +5295,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4366</v>
+        <v>1962</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5323,10 +5323,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544594</v>
+        <v>544660</v>
       </c>
       <c r="R40" t="n">
-        <v>6961545</v>
+        <v>6961435</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5385,10 +5385,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119625612</v>
+        <v>119625601</v>
       </c>
       <c r="B41" t="n">
-        <v>91884</v>
+        <v>56522</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5397,38 +5397,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5449</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>544836</v>
+        <v>545027</v>
       </c>
       <c r="R41" t="n">
-        <v>6961292</v>
+        <v>6961112</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5487,10 +5491,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119625393</v>
+        <v>119625384</v>
       </c>
       <c r="B42" t="n">
-        <v>89633</v>
+        <v>91858</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5503,21 +5507,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1962</v>
+        <v>4368</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5527,10 +5531,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544660</v>
+        <v>544582</v>
       </c>
       <c r="R42" t="n">
-        <v>6961435</v>
+        <v>6961543</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5589,7 +5593,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119625599</v>
+        <v>119625396</v>
       </c>
       <c r="B43" t="n">
         <v>91834</v>
@@ -5629,10 +5633,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>545111</v>
+        <v>544660</v>
       </c>
       <c r="R43" t="n">
-        <v>6961107</v>
+        <v>6961435</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5691,7 +5695,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119625615</v>
+        <v>119625606</v>
       </c>
       <c r="B44" t="n">
         <v>91840</v>
@@ -5731,10 +5735,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544748</v>
+        <v>544967</v>
       </c>
       <c r="R44" t="n">
-        <v>6961477</v>
+        <v>6961196</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5775,6 +5779,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5793,10 +5798,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119625398</v>
+        <v>119625591</v>
       </c>
       <c r="B45" t="n">
-        <v>78171</v>
+        <v>91834</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5809,21 +5814,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5833,10 +5838,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>544657</v>
+        <v>545162</v>
       </c>
       <c r="R45" t="n">
-        <v>6961420</v>
+        <v>6961129</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5877,6 +5882,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5895,10 +5901,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119625579</v>
+        <v>119625377</v>
       </c>
       <c r="B46" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5911,21 +5917,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5935,10 +5941,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>545270</v>
+        <v>544634</v>
       </c>
       <c r="R46" t="n">
-        <v>6960997</v>
+        <v>6961537</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5997,10 +6003,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119625591</v>
+        <v>119625575</v>
       </c>
       <c r="B47" t="n">
-        <v>91834</v>
+        <v>89252</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6009,25 +6015,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6037,10 +6043,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>545162</v>
+        <v>545016</v>
       </c>
       <c r="R47" t="n">
-        <v>6961129</v>
+        <v>6960898</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6081,7 +6087,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6100,10 +6105,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119625384</v>
+        <v>119625381</v>
       </c>
       <c r="B48" t="n">
-        <v>91858</v>
+        <v>91840</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6112,25 +6117,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4368</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6140,10 +6145,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>544582</v>
+        <v>544635</v>
       </c>
       <c r="R48" t="n">
-        <v>6961543</v>
+        <v>6961580</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6202,10 +6207,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119625386</v>
+        <v>119625378</v>
       </c>
       <c r="B49" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6214,25 +6219,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6242,10 +6247,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>544563</v>
+        <v>544666</v>
       </c>
       <c r="R49" t="n">
-        <v>6961544</v>
+        <v>6961642</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6304,10 +6309,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119625592</v>
+        <v>119625580</v>
       </c>
       <c r="B50" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6320,21 +6325,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6344,10 +6349,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>545146</v>
+        <v>545279</v>
       </c>
       <c r="R50" t="n">
-        <v>6961121</v>
+        <v>6961027</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6406,10 +6411,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119625385</v>
+        <v>119625380</v>
       </c>
       <c r="B51" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6422,21 +6427,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6446,10 +6451,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>544570</v>
+        <v>544678</v>
       </c>
       <c r="R51" t="n">
-        <v>6961546</v>
+        <v>6961634</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6508,10 +6513,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119625373</v>
+        <v>119625612</v>
       </c>
       <c r="B52" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6524,21 +6529,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6548,10 +6553,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>544694</v>
+        <v>544836</v>
       </c>
       <c r="R52" t="n">
-        <v>6961492</v>
+        <v>6961292</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6610,10 +6615,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119625381</v>
+        <v>119625383</v>
       </c>
       <c r="B53" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6626,21 +6631,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6650,10 +6655,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>544635</v>
+        <v>544594</v>
       </c>
       <c r="R53" t="n">
-        <v>6961580</v>
+        <v>6961545</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6712,10 +6717,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119625574</v>
+        <v>119625390</v>
       </c>
       <c r="B54" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6724,25 +6729,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6752,10 +6757,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>544964</v>
+        <v>544640</v>
       </c>
       <c r="R54" t="n">
-        <v>6960939</v>
+        <v>6961471</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6814,10 +6819,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119625392</v>
+        <v>119625373</v>
       </c>
       <c r="B55" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6830,21 +6835,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6854,10 +6859,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>544655</v>
+        <v>544694</v>
       </c>
       <c r="R55" t="n">
-        <v>6961452</v>
+        <v>6961492</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6916,10 +6921,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119625597</v>
+        <v>119625392</v>
       </c>
       <c r="B56" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6932,21 +6937,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6956,10 +6961,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>545109</v>
+        <v>544655</v>
       </c>
       <c r="R56" t="n">
-        <v>6961124</v>
+        <v>6961452</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7018,10 +7023,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119625582</v>
+        <v>119625388</v>
       </c>
       <c r="B57" t="n">
-        <v>91834</v>
+        <v>78526</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7034,21 +7039,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7058,10 +7063,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>545184</v>
+        <v>544609</v>
       </c>
       <c r="R57" t="n">
-        <v>6961041</v>
+        <v>6961486</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7120,7 +7125,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119625576</v>
+        <v>119625579</v>
       </c>
       <c r="B58" t="n">
         <v>91834</v>
@@ -7160,10 +7165,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>545048</v>
+        <v>545270</v>
       </c>
       <c r="R58" t="n">
-        <v>6960895</v>
+        <v>6960997</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7222,10 +7227,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119625598</v>
+        <v>119625584</v>
       </c>
       <c r="B59" t="n">
-        <v>91834</v>
+        <v>89230</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7234,25 +7239,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4362</v>
+        <v>1596</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7262,10 +7267,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>545110</v>
+        <v>545189</v>
       </c>
       <c r="R59" t="n">
-        <v>6961114</v>
+        <v>6961120</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7324,7 +7329,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119625396</v>
+        <v>119625576</v>
       </c>
       <c r="B60" t="n">
         <v>91834</v>
@@ -7364,10 +7369,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>544660</v>
+        <v>545048</v>
       </c>
       <c r="R60" t="n">
-        <v>6961435</v>
+        <v>6960895</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7426,10 +7431,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119625585</v>
+        <v>119625583</v>
       </c>
       <c r="B61" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7442,21 +7447,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7466,10 +7471,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>545189</v>
+        <v>545192</v>
       </c>
       <c r="R61" t="n">
-        <v>6961131</v>
+        <v>6961119</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7528,10 +7533,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119625603</v>
+        <v>119625574</v>
       </c>
       <c r="B62" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7544,21 +7549,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7568,10 +7573,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>544968</v>
+        <v>544964</v>
       </c>
       <c r="R62" t="n">
-        <v>6961151</v>
+        <v>6960939</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7630,10 +7635,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119625607</v>
+        <v>119625597</v>
       </c>
       <c r="B63" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7642,25 +7647,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7670,10 +7675,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>544911</v>
+        <v>545109</v>
       </c>
       <c r="R63" t="n">
-        <v>6961201</v>
+        <v>6961124</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7732,10 +7737,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119625378</v>
+        <v>119625387</v>
       </c>
       <c r="B64" t="n">
-        <v>91840</v>
+        <v>77910</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7744,25 +7749,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7772,10 +7777,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>544666</v>
+        <v>544571</v>
       </c>
       <c r="R64" t="n">
-        <v>6961642</v>
+        <v>6961517</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7834,10 +7839,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119625387</v>
+        <v>119625386</v>
       </c>
       <c r="B65" t="n">
-        <v>77910</v>
+        <v>91856</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7850,21 +7855,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6437</v>
+        <v>2059</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7874,10 +7879,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>544571</v>
+        <v>544563</v>
       </c>
       <c r="R65" t="n">
-        <v>6961517</v>
+        <v>6961544</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7936,10 +7941,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119625584</v>
+        <v>119625615</v>
       </c>
       <c r="B66" t="n">
-        <v>89230</v>
+        <v>91840</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7948,25 +7953,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1596</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7976,10 +7981,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>545189</v>
+        <v>544748</v>
       </c>
       <c r="R66" t="n">
-        <v>6961120</v>
+        <v>6961477</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8038,10 +8043,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119625391</v>
+        <v>119625592</v>
       </c>
       <c r="B67" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8050,25 +8055,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8078,10 +8083,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>544660</v>
+        <v>545146</v>
       </c>
       <c r="R67" t="n">
-        <v>6961476</v>
+        <v>6961121</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8140,10 +8145,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119625580</v>
+        <v>119625391</v>
       </c>
       <c r="B68" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8152,25 +8157,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8180,10 +8185,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>545279</v>
+        <v>544660</v>
       </c>
       <c r="R68" t="n">
-        <v>6961027</v>
+        <v>6961476</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8242,10 +8247,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119625380</v>
+        <v>119625582</v>
       </c>
       <c r="B69" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8258,21 +8263,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8282,10 +8287,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>544678</v>
+        <v>545184</v>
       </c>
       <c r="R69" t="n">
-        <v>6961634</v>
+        <v>6961041</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8344,10 +8349,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119625583</v>
+        <v>119625585</v>
       </c>
       <c r="B70" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8360,21 +8365,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8384,10 +8389,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>545192</v>
+        <v>545189</v>
       </c>
       <c r="R70" t="n">
-        <v>6961119</v>
+        <v>6961131</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8446,10 +8451,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119625388</v>
+        <v>119625599</v>
       </c>
       <c r="B71" t="n">
-        <v>78526</v>
+        <v>91834</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8462,21 +8467,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8486,10 +8491,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>544609</v>
+        <v>545111</v>
       </c>
       <c r="R71" t="n">
-        <v>6961486</v>
+        <v>6961107</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8548,10 +8553,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119625601</v>
+        <v>119625603</v>
       </c>
       <c r="B72" t="n">
-        <v>56522</v>
+        <v>91884</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8560,42 +8565,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100138</v>
+        <v>5449</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>545027</v>
+        <v>544968</v>
       </c>
       <c r="R72" t="n">
-        <v>6961112</v>
+        <v>6961151</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8654,10 +8655,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119625596</v>
+        <v>119625581</v>
       </c>
       <c r="B73" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8670,21 +8671,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8694,10 +8695,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>545102</v>
+        <v>545208</v>
       </c>
       <c r="R73" t="n">
-        <v>6961133</v>
+        <v>6961020</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8756,10 +8757,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119625593</v>
+        <v>119625594</v>
       </c>
       <c r="B74" t="n">
-        <v>91826</v>
+        <v>91834</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8772,21 +8773,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8858,10 +8859,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119625395</v>
+        <v>119625382</v>
       </c>
       <c r="B75" t="n">
-        <v>91840</v>
+        <v>90807</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8870,25 +8871,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8898,10 +8899,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>544660</v>
+        <v>544614</v>
       </c>
       <c r="R75" t="n">
-        <v>6961435</v>
+        <v>6961561</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8960,10 +8961,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119625377</v>
+        <v>119625593</v>
       </c>
       <c r="B76" t="n">
-        <v>91832</v>
+        <v>91826</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8976,21 +8977,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9000,10 +9001,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>544634</v>
+        <v>545146</v>
       </c>
       <c r="R76" t="n">
-        <v>6961537</v>
+        <v>6961121</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9062,7 +9063,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119625594</v>
+        <v>119625385</v>
       </c>
       <c r="B77" t="n">
         <v>91834</v>
@@ -9102,10 +9103,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>545146</v>
+        <v>544570</v>
       </c>
       <c r="R77" t="n">
-        <v>6961121</v>
+        <v>6961546</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9164,10 +9165,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119625578</v>
+        <v>119625398</v>
       </c>
       <c r="B78" t="n">
-        <v>91834</v>
+        <v>78171</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9180,21 +9181,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9204,10 +9205,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>545085</v>
+        <v>544657</v>
       </c>
       <c r="R78" t="n">
-        <v>6960933</v>
+        <v>6961420</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9266,10 +9267,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119625581</v>
+        <v>119625596</v>
       </c>
       <c r="B79" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9282,21 +9283,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9306,10 +9307,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>545208</v>
+        <v>545102</v>
       </c>
       <c r="R79" t="n">
-        <v>6961020</v>
+        <v>6961133</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9368,10 +9369,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119625382</v>
+        <v>119625395</v>
       </c>
       <c r="B80" t="n">
-        <v>90807</v>
+        <v>91840</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9380,25 +9381,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9408,10 +9409,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>544614</v>
+        <v>544660</v>
       </c>
       <c r="R80" t="n">
-        <v>6961561</v>
+        <v>6961435</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9470,7 +9471,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119625606</v>
+        <v>119625607</v>
       </c>
       <c r="B81" t="n">
         <v>91840</v>
@@ -9510,10 +9511,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>544967</v>
+        <v>544911</v>
       </c>
       <c r="R81" t="n">
-        <v>6961196</v>
+        <v>6961201</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9554,7 +9555,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9573,10 +9573,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119625575</v>
+        <v>119625374</v>
       </c>
       <c r="B82" t="n">
-        <v>89252</v>
+        <v>91840</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9585,25 +9585,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9613,10 +9613,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>545016</v>
+        <v>544655</v>
       </c>
       <c r="R82" t="n">
-        <v>6960898</v>
+        <v>6961490</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9675,10 +9675,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119625374</v>
+        <v>119625598</v>
       </c>
       <c r="B83" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9687,25 +9687,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9715,10 +9715,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>544655</v>
+        <v>545110</v>
       </c>
       <c r="R83" t="n">
-        <v>6961490</v>
+        <v>6961114</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9777,10 +9777,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119625390</v>
+        <v>119625578</v>
       </c>
       <c r="B84" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9789,25 +9789,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>544640</v>
+        <v>545085</v>
       </c>
       <c r="R84" t="n">
-        <v>6961471</v>
+        <v>6960933</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>

--- a/artfynd/A 50503-2023 artfynd.xlsx
+++ b/artfynd/A 50503-2023 artfynd.xlsx
@@ -7635,10 +7635,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119625597</v>
+        <v>119625387</v>
       </c>
       <c r="B63" t="n">
-        <v>91856</v>
+        <v>77910</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7651,21 +7651,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2059</v>
+        <v>6437</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7675,10 +7675,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>545109</v>
+        <v>544571</v>
       </c>
       <c r="R63" t="n">
-        <v>6961124</v>
+        <v>6961517</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7737,10 +7737,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119625387</v>
+        <v>119625597</v>
       </c>
       <c r="B64" t="n">
-        <v>77910</v>
+        <v>91856</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7753,21 +7753,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6437</v>
+        <v>2059</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7777,10 +7777,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>544571</v>
+        <v>545109</v>
       </c>
       <c r="R64" t="n">
-        <v>6961517</v>
+        <v>6961124</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>

--- a/artfynd/A 50503-2023 artfynd.xlsx
+++ b/artfynd/A 50503-2023 artfynd.xlsx
@@ -5283,10 +5283,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119625393</v>
+        <v>119625395</v>
       </c>
       <c r="B40" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5295,25 +5295,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5385,10 +5385,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119625601</v>
+        <v>119625575</v>
       </c>
       <c r="B41" t="n">
-        <v>56522</v>
+        <v>89252</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5397,42 +5397,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>6276</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>545027</v>
+        <v>545016</v>
       </c>
       <c r="R41" t="n">
-        <v>6961112</v>
+        <v>6960898</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5491,10 +5487,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119625384</v>
+        <v>119625574</v>
       </c>
       <c r="B42" t="n">
-        <v>91858</v>
+        <v>91834</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5507,21 +5503,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4368</v>
+        <v>4362</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5531,10 +5527,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544582</v>
+        <v>544964</v>
       </c>
       <c r="R42" t="n">
-        <v>6961543</v>
+        <v>6960939</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5593,10 +5589,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119625396</v>
+        <v>119625597</v>
       </c>
       <c r="B43" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5609,21 +5605,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5633,10 +5629,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544660</v>
+        <v>545109</v>
       </c>
       <c r="R43" t="n">
-        <v>6961435</v>
+        <v>6961124</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5695,10 +5691,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119625606</v>
+        <v>119625380</v>
       </c>
       <c r="B44" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5707,25 +5703,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5735,10 +5731,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544967</v>
+        <v>544678</v>
       </c>
       <c r="R44" t="n">
-        <v>6961196</v>
+        <v>6961634</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5779,7 +5775,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5798,7 +5793,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119625591</v>
+        <v>119625599</v>
       </c>
       <c r="B45" t="n">
         <v>91834</v>
@@ -5838,10 +5833,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>545162</v>
+        <v>545111</v>
       </c>
       <c r="R45" t="n">
-        <v>6961129</v>
+        <v>6961107</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5882,7 +5877,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5901,10 +5895,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119625377</v>
+        <v>119625612</v>
       </c>
       <c r="B46" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5917,21 +5911,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5941,10 +5935,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544634</v>
+        <v>544836</v>
       </c>
       <c r="R46" t="n">
-        <v>6961537</v>
+        <v>6961292</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -6003,10 +5997,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119625575</v>
+        <v>119625382</v>
       </c>
       <c r="B47" t="n">
-        <v>89252</v>
+        <v>90807</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6019,21 +6013,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6276</v>
+        <v>65</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6043,10 +6037,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>545016</v>
+        <v>544614</v>
       </c>
       <c r="R47" t="n">
-        <v>6960898</v>
+        <v>6961561</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6105,10 +6099,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119625381</v>
+        <v>119625383</v>
       </c>
       <c r="B48" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6121,21 +6115,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6145,10 +6139,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>544635</v>
+        <v>544594</v>
       </c>
       <c r="R48" t="n">
-        <v>6961580</v>
+        <v>6961545</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6207,10 +6201,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119625378</v>
+        <v>119625585</v>
       </c>
       <c r="B49" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6219,25 +6213,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6247,10 +6241,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>544666</v>
+        <v>545189</v>
       </c>
       <c r="R49" t="n">
-        <v>6961642</v>
+        <v>6961131</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6309,10 +6303,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119625580</v>
+        <v>119625391</v>
       </c>
       <c r="B50" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6321,25 +6315,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6349,10 +6343,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>545279</v>
+        <v>544660</v>
       </c>
       <c r="R50" t="n">
-        <v>6961027</v>
+        <v>6961476</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6411,10 +6405,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119625380</v>
+        <v>119625606</v>
       </c>
       <c r="B51" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6423,25 +6417,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6451,10 +6445,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>544678</v>
+        <v>544967</v>
       </c>
       <c r="R51" t="n">
-        <v>6961634</v>
+        <v>6961196</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6495,6 +6489,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6513,10 +6508,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119625612</v>
+        <v>119625377</v>
       </c>
       <c r="B52" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6529,21 +6524,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6553,10 +6548,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>544836</v>
+        <v>544634</v>
       </c>
       <c r="R52" t="n">
-        <v>6961292</v>
+        <v>6961537</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6615,7 +6610,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119625383</v>
+        <v>119625390</v>
       </c>
       <c r="B53" t="n">
         <v>91852</v>
@@ -6655,10 +6650,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>544594</v>
+        <v>544640</v>
       </c>
       <c r="R53" t="n">
-        <v>6961545</v>
+        <v>6961471</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6717,10 +6712,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119625390</v>
+        <v>119625386</v>
       </c>
       <c r="B54" t="n">
-        <v>91852</v>
+        <v>91856</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6729,25 +6724,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6757,10 +6752,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>544640</v>
+        <v>544563</v>
       </c>
       <c r="R54" t="n">
-        <v>6961471</v>
+        <v>6961544</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6819,10 +6814,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119625373</v>
+        <v>119625393</v>
       </c>
       <c r="B55" t="n">
-        <v>91856</v>
+        <v>89633</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6835,21 +6830,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6859,10 +6854,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>544694</v>
+        <v>544660</v>
       </c>
       <c r="R55" t="n">
-        <v>6961492</v>
+        <v>6961435</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6921,10 +6916,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119625392</v>
+        <v>119625374</v>
       </c>
       <c r="B56" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6933,25 +6928,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6964,7 +6959,7 @@
         <v>544655</v>
       </c>
       <c r="R56" t="n">
-        <v>6961452</v>
+        <v>6961490</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7023,10 +7018,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119625388</v>
+        <v>119625607</v>
       </c>
       <c r="B57" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7035,25 +7030,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7063,10 +7058,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>544609</v>
+        <v>544911</v>
       </c>
       <c r="R57" t="n">
-        <v>6961486</v>
+        <v>6961201</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7125,7 +7120,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119625579</v>
+        <v>119625591</v>
       </c>
       <c r="B58" t="n">
         <v>91834</v>
@@ -7165,10 +7160,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>545270</v>
+        <v>545162</v>
       </c>
       <c r="R58" t="n">
-        <v>6960997</v>
+        <v>6961129</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7209,6 +7204,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7227,10 +7223,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119625584</v>
+        <v>119625594</v>
       </c>
       <c r="B59" t="n">
-        <v>89230</v>
+        <v>91834</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7239,25 +7235,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1596</v>
+        <v>4362</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7267,10 +7263,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>545189</v>
+        <v>545146</v>
       </c>
       <c r="R59" t="n">
-        <v>6961120</v>
+        <v>6961121</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7329,10 +7325,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119625576</v>
+        <v>119625603</v>
       </c>
       <c r="B60" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7345,21 +7341,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7369,10 +7365,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>545048</v>
+        <v>544968</v>
       </c>
       <c r="R60" t="n">
-        <v>6960895</v>
+        <v>6961151</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7431,10 +7427,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119625583</v>
+        <v>119625392</v>
       </c>
       <c r="B61" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7447,21 +7443,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7471,10 +7467,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>545192</v>
+        <v>544655</v>
       </c>
       <c r="R61" t="n">
-        <v>6961119</v>
+        <v>6961452</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7533,10 +7529,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119625574</v>
+        <v>119625381</v>
       </c>
       <c r="B62" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7545,25 +7541,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7573,10 +7569,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>544964</v>
+        <v>544635</v>
       </c>
       <c r="R62" t="n">
-        <v>6960939</v>
+        <v>6961580</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7635,10 +7631,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119625387</v>
+        <v>119625378</v>
       </c>
       <c r="B63" t="n">
-        <v>77910</v>
+        <v>91840</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7647,25 +7643,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7675,10 +7671,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>544571</v>
+        <v>544666</v>
       </c>
       <c r="R63" t="n">
-        <v>6961517</v>
+        <v>6961642</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7737,10 +7733,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119625597</v>
+        <v>119625592</v>
       </c>
       <c r="B64" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7753,21 +7749,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7777,10 +7773,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>545109</v>
+        <v>545146</v>
       </c>
       <c r="R64" t="n">
-        <v>6961124</v>
+        <v>6961121</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7839,10 +7835,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119625386</v>
+        <v>119625581</v>
       </c>
       <c r="B65" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7855,21 +7851,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7879,10 +7875,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>544563</v>
+        <v>545208</v>
       </c>
       <c r="R65" t="n">
-        <v>6961544</v>
+        <v>6961020</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7941,10 +7937,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119625615</v>
+        <v>119625579</v>
       </c>
       <c r="B66" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7953,25 +7949,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7981,10 +7977,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>544748</v>
+        <v>545270</v>
       </c>
       <c r="R66" t="n">
-        <v>6961477</v>
+        <v>6960997</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8043,10 +8039,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119625592</v>
+        <v>119625578</v>
       </c>
       <c r="B67" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8059,21 +8055,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8083,10 +8079,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>545146</v>
+        <v>545085</v>
       </c>
       <c r="R67" t="n">
-        <v>6961121</v>
+        <v>6960933</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8145,10 +8141,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119625391</v>
+        <v>119625601</v>
       </c>
       <c r="B68" t="n">
-        <v>91840</v>
+        <v>56522</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8161,34 +8157,38 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>544660</v>
+        <v>545027</v>
       </c>
       <c r="R68" t="n">
-        <v>6961476</v>
+        <v>6961112</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8247,10 +8247,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119625582</v>
+        <v>119625388</v>
       </c>
       <c r="B69" t="n">
-        <v>91834</v>
+        <v>78526</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8263,21 +8263,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8287,10 +8287,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>545184</v>
+        <v>544609</v>
       </c>
       <c r="R69" t="n">
-        <v>6961041</v>
+        <v>6961486</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8349,10 +8349,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119625585</v>
+        <v>119625384</v>
       </c>
       <c r="B70" t="n">
-        <v>91834</v>
+        <v>91858</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8365,21 +8365,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4362</v>
+        <v>4368</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8389,10 +8389,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>545189</v>
+        <v>544582</v>
       </c>
       <c r="R70" t="n">
-        <v>6961131</v>
+        <v>6961543</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8451,7 +8451,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119625599</v>
+        <v>119625576</v>
       </c>
       <c r="B71" t="n">
         <v>91834</v>
@@ -8491,10 +8491,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>545111</v>
+        <v>545048</v>
       </c>
       <c r="R71" t="n">
-        <v>6961107</v>
+        <v>6960895</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8553,10 +8553,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119625603</v>
+        <v>119625584</v>
       </c>
       <c r="B72" t="n">
-        <v>91884</v>
+        <v>89230</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8565,25 +8565,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5449</v>
+        <v>1596</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8593,10 +8593,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>544968</v>
+        <v>545189</v>
       </c>
       <c r="R72" t="n">
-        <v>6961151</v>
+        <v>6961120</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8655,10 +8655,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119625581</v>
+        <v>119625373</v>
       </c>
       <c r="B73" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8671,21 +8671,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8695,10 +8695,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>545208</v>
+        <v>544694</v>
       </c>
       <c r="R73" t="n">
-        <v>6961020</v>
+        <v>6961492</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8757,10 +8757,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119625594</v>
+        <v>119625398</v>
       </c>
       <c r="B74" t="n">
-        <v>91834</v>
+        <v>78171</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8773,21 +8773,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8797,10 +8797,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>545146</v>
+        <v>544657</v>
       </c>
       <c r="R74" t="n">
-        <v>6961121</v>
+        <v>6961420</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8859,10 +8859,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119625382</v>
+        <v>119625582</v>
       </c>
       <c r="B75" t="n">
-        <v>90807</v>
+        <v>91834</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8871,25 +8871,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>65</v>
+        <v>4362</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8899,10 +8899,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>544614</v>
+        <v>545184</v>
       </c>
       <c r="R75" t="n">
-        <v>6961561</v>
+        <v>6961041</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8961,10 +8961,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119625593</v>
+        <v>119625583</v>
       </c>
       <c r="B76" t="n">
-        <v>91826</v>
+        <v>91856</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8977,21 +8977,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3100</v>
+        <v>2059</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9001,10 +9001,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>545146</v>
+        <v>545192</v>
       </c>
       <c r="R76" t="n">
-        <v>6961121</v>
+        <v>6961119</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9063,10 +9063,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119625385</v>
+        <v>119625593</v>
       </c>
       <c r="B77" t="n">
-        <v>91834</v>
+        <v>91826</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9079,21 +9079,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9103,10 +9103,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>544570</v>
+        <v>545146</v>
       </c>
       <c r="R77" t="n">
-        <v>6961546</v>
+        <v>6961121</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9165,10 +9165,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119625398</v>
+        <v>119625596</v>
       </c>
       <c r="B78" t="n">
-        <v>78171</v>
+        <v>91834</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9181,21 +9181,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9205,10 +9205,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>544657</v>
+        <v>545102</v>
       </c>
       <c r="R78" t="n">
-        <v>6961420</v>
+        <v>6961133</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9267,7 +9267,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119625596</v>
+        <v>119625396</v>
       </c>
       <c r="B79" t="n">
         <v>91834</v>
@@ -9307,10 +9307,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>545102</v>
+        <v>544660</v>
       </c>
       <c r="R79" t="n">
-        <v>6961133</v>
+        <v>6961435</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9369,10 +9369,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119625395</v>
+        <v>119625387</v>
       </c>
       <c r="B80" t="n">
-        <v>91840</v>
+        <v>77910</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9381,25 +9381,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9409,10 +9409,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>544660</v>
+        <v>544571</v>
       </c>
       <c r="R80" t="n">
-        <v>6961435</v>
+        <v>6961517</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9471,10 +9471,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119625607</v>
+        <v>119625580</v>
       </c>
       <c r="B81" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9483,25 +9483,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9511,10 +9511,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>544911</v>
+        <v>545279</v>
       </c>
       <c r="R81" t="n">
-        <v>6961201</v>
+        <v>6961027</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9573,10 +9573,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119625374</v>
+        <v>119625385</v>
       </c>
       <c r="B82" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9585,25 +9585,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9613,10 +9613,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>544655</v>
+        <v>544570</v>
       </c>
       <c r="R82" t="n">
-        <v>6961490</v>
+        <v>6961546</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9777,10 +9777,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119625578</v>
+        <v>119625615</v>
       </c>
       <c r="B84" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9789,25 +9789,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>545085</v>
+        <v>544748</v>
       </c>
       <c r="R84" t="n">
-        <v>6960933</v>
+        <v>6961477</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>

--- a/artfynd/A 50503-2023 artfynd.xlsx
+++ b/artfynd/A 50503-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY84"/>
+  <dimension ref="A1:AY96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104000076</v>
+        <v>128369903</v>
       </c>
       <c r="B2" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>Gustavsnäs, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545010.0221869214</v>
+        <v>545259</v>
       </c>
       <c r="R2" t="n">
-        <v>6961039.07386395</v>
+        <v>6960474</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,78 +760,64 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104000042</v>
+        <v>119625382</v>
       </c>
       <c r="B3" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storflobäcken, Jmt</t>
+          <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545090.3018512697</v>
+        <v>544614</v>
       </c>
       <c r="R3" t="n">
-        <v>6960936.229350298</v>
+        <v>6961561</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,62 +857,48 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104000186</v>
+        <v>104000103</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544912.8828501732</v>
+        <v>544954</v>
       </c>
       <c r="R4" t="n">
-        <v>6961201.668727844</v>
+        <v>6961093</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +943,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +953,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,15 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104000185</v>
+        <v>104000147</v>
       </c>
       <c r="B5" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1078,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544628.9189383922</v>
+        <v>544884</v>
       </c>
       <c r="R5" t="n">
-        <v>6961516.009038877</v>
+        <v>6961026</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1059,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1069,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,15 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104000113</v>
+        <v>104000166</v>
       </c>
       <c r="B6" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,34 +1116,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Småmyrorna, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544931.5690506987</v>
+        <v>544684</v>
       </c>
       <c r="R6" t="n">
-        <v>6960572.286650707</v>
+        <v>6961438</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,7 +1175,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1185,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,53 +1221,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104000083</v>
+        <v>119625398</v>
       </c>
       <c r="B7" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4365</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544581.3394257053</v>
+        <v>544657</v>
       </c>
       <c r="R7" t="n">
-        <v>6961508.496053636</v>
+        <v>6961420</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1350,22 +1286,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,40 +1302,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104000044</v>
+        <v>104000128</v>
       </c>
       <c r="B8" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,21 +1329,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1441,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544684.215671078</v>
+        <v>544971</v>
       </c>
       <c r="R8" t="n">
-        <v>6961326.755374322</v>
+        <v>6961065</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1388,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1398,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1522,50 +1434,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104000173</v>
+        <v>104000047</v>
       </c>
       <c r="B9" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90659</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>1593</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Storflobäcken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545110.6379008115</v>
+        <v>544944</v>
       </c>
       <c r="R9" t="n">
-        <v>6960891.174662136</v>
+        <v>6960924</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1597,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1607,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1643,37 +1550,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104000188</v>
+        <v>104000056</v>
       </c>
       <c r="B10" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>1593</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1683,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544831.3494682688</v>
+        <v>544858</v>
       </c>
       <c r="R10" t="n">
-        <v>6961262.826330876</v>
+        <v>6961333</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1718,7 +1620,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1728,7 +1630,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1764,53 +1666,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104000128</v>
+        <v>119625584</v>
       </c>
       <c r="B11" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90674</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1596</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544971.6008178937</v>
+        <v>545189</v>
       </c>
       <c r="R11" t="n">
-        <v>6961065.563996335</v>
+        <v>6961120</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1834,22 +1731,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:28</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:28</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1860,40 +1747,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104000158</v>
+        <v>119625393</v>
       </c>
       <c r="B12" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1901,37 +1774,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544686.3024396474</v>
+        <v>544660</v>
       </c>
       <c r="R12" t="n">
-        <v>6961341.892949275</v>
+        <v>6961435</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1955,22 +1828,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1981,62 +1844,48 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104000059</v>
+        <v>104000116</v>
       </c>
       <c r="B13" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2046,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544562.4639637915</v>
+        <v>544823</v>
       </c>
       <c r="R13" t="n">
-        <v>6961548.071146769</v>
+        <v>6961276</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2081,7 +1930,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2091,7 +1940,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2127,37 +1976,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104000107</v>
+        <v>104000176</v>
       </c>
       <c r="B14" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2167,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544826.6500468121</v>
+        <v>544878</v>
       </c>
       <c r="R14" t="n">
-        <v>6961237.579558824</v>
+        <v>6960964</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2202,7 +2046,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2212,7 +2056,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2248,53 +2092,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104000201</v>
+        <v>119625373</v>
       </c>
       <c r="B15" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544654.3874811238</v>
+        <v>544694</v>
       </c>
       <c r="R15" t="n">
-        <v>6961328.639405134</v>
+        <v>6961492</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2318,22 +2157,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:32</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:32</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2344,78 +2173,64 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104000159</v>
+        <v>119625380</v>
       </c>
       <c r="B16" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6437</v>
+        <v>2059</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544576.1729893234</v>
+        <v>544678</v>
       </c>
       <c r="R16" t="n">
-        <v>6961517.582593298</v>
+        <v>6961634</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2439,22 +2254,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2465,40 +2270,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104000047</v>
+        <v>119625386</v>
       </c>
       <c r="B17" t="n">
-        <v>87979</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2506,37 +2297,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1593</v>
+        <v>2059</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544944.1870359139</v>
+        <v>544563</v>
       </c>
       <c r="R17" t="n">
-        <v>6960924.15499141</v>
+        <v>6961544</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2560,22 +2351,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:57</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:57</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2586,78 +2367,64 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104000092</v>
+        <v>119625583</v>
       </c>
       <c r="B18" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544973.5571266026</v>
+        <v>545192</v>
       </c>
       <c r="R18" t="n">
-        <v>6960989.579556035</v>
+        <v>6961119</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2681,22 +2448,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>17:11</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>17:11</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2707,78 +2464,64 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104000171</v>
+        <v>119625589</v>
       </c>
       <c r="B19" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544671.1468427742</v>
+        <v>545169</v>
       </c>
       <c r="R19" t="n">
-        <v>6961512.46207581</v>
+        <v>6961145</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2802,22 +2545,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:21</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:21</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2828,78 +2561,64 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104000170</v>
+        <v>119625597</v>
       </c>
       <c r="B20" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544815.9343842064</v>
+        <v>545109</v>
       </c>
       <c r="R20" t="n">
-        <v>6961283.677926547</v>
+        <v>6961124</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2923,22 +2642,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:59</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:59</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2949,40 +2658,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>104000139</v>
+        <v>104000154</v>
       </c>
       <c r="B21" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2990,21 +2685,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>3100</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3014,10 +2709,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544676.2824500414</v>
+        <v>544717</v>
       </c>
       <c r="R21" t="n">
-        <v>6961505.66440048</v>
+        <v>6961627</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3049,7 +2744,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3059,7 +2754,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3095,15 +2790,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104000141</v>
+        <v>119625593</v>
       </c>
       <c r="B22" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,37 +2801,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Småmyrorna, Jmt</t>
+          <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544830.0066941141</v>
+        <v>545146</v>
       </c>
       <c r="R22" t="n">
-        <v>6961125.903394392</v>
+        <v>6961121</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3165,22 +2855,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:19</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:19</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3191,40 +2871,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>104000166</v>
+        <v>104000042</v>
       </c>
       <c r="B23" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3232,34 +2898,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>Storflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544684.0790951664</v>
+        <v>545090</v>
       </c>
       <c r="R23" t="n">
-        <v>6961438.010651757</v>
+        <v>6960936</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3291,7 +2957,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3301,7 +2967,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3337,15 +3003,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>104000122</v>
+        <v>104000105</v>
       </c>
       <c r="B24" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3353,21 +3014,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3377,10 +3038,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544854.0144480224</v>
+        <v>544836</v>
       </c>
       <c r="R24" t="n">
-        <v>6961113.867894865</v>
+        <v>6961009</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3412,7 +3073,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3422,7 +3083,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3433,11 +3094,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
@@ -3463,37 +3119,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>104000175</v>
+        <v>104000112</v>
       </c>
       <c r="B25" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3503,10 +3154,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544695.5805868517</v>
+        <v>544582</v>
       </c>
       <c r="R25" t="n">
-        <v>6961468.842167489</v>
+        <v>6961502</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3538,7 +3189,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3548,7 +3199,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3584,50 +3235,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>104000056</v>
+        <v>104000141</v>
       </c>
       <c r="B26" t="n">
-        <v>87979</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1593</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>Småmyrorna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544858.3578587895</v>
+        <v>544830</v>
       </c>
       <c r="R26" t="n">
-        <v>6961333.247391423</v>
+        <v>6961126</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3659,7 +3305,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3669,7 +3315,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3705,50 +3351,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>104000157</v>
+        <v>104000146</v>
       </c>
       <c r="B27" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>Småmyrorna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544573.6389992632</v>
+        <v>544847</v>
       </c>
       <c r="R27" t="n">
-        <v>6961535.403521274</v>
+        <v>6961148</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3780,7 +3421,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3790,7 +3431,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3826,15 +3467,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>104000105</v>
+        <v>104000158</v>
       </c>
       <c r="B28" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3866,10 +3502,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544836.189176211</v>
+        <v>544686</v>
       </c>
       <c r="R28" t="n">
-        <v>6961008.767170357</v>
+        <v>6961342</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3901,7 +3537,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3911,7 +3547,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3947,15 +3583,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>104000048</v>
+        <v>119625377</v>
       </c>
       <c r="B29" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3963,37 +3594,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544898.6565513101</v>
+        <v>544634</v>
       </c>
       <c r="R29" t="n">
-        <v>6960967.492360881</v>
+        <v>6961537</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4017,22 +3648,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:52</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:52</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4043,40 +3664,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AS29" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>104000116</v>
+        <v>119625581</v>
       </c>
       <c r="B30" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4084,37 +3691,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544822.9230617819</v>
+        <v>545208</v>
       </c>
       <c r="R30" t="n">
-        <v>6961275.531656257</v>
+        <v>6961020</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4138,22 +3745,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:58</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:58</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4164,78 +3761,64 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AS30" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>104000192</v>
+        <v>119625592</v>
       </c>
       <c r="B31" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Småmyrorna, Jmt</t>
+          <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544646.0552056613</v>
+        <v>545146</v>
       </c>
       <c r="R31" t="n">
-        <v>6961199.408444637</v>
+        <v>6961121</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4259,22 +3842,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4285,40 +3858,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AS31" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>104000103</v>
+        <v>104000044</v>
       </c>
       <c r="B32" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4326,21 +3885,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4350,10 +3909,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544954.2562446241</v>
+        <v>544684</v>
       </c>
       <c r="R32" t="n">
-        <v>6961093.258208943</v>
+        <v>6961327</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4385,7 +3944,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4395,7 +3954,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4431,15 +3990,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>104000147</v>
+        <v>104000048</v>
       </c>
       <c r="B33" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4447,21 +4001,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4471,10 +4025,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544884.1088988176</v>
+        <v>544899</v>
       </c>
       <c r="R33" t="n">
-        <v>6961025.447405947</v>
+        <v>6960968</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4506,7 +4060,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4516,7 +4070,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4552,15 +4106,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>104000095</v>
+        <v>104000050</v>
       </c>
       <c r="B34" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4568,34 +4117,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Våtflobäcken, Jmt</t>
+          <t>Storflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>545032.3180707665</v>
+        <v>545195</v>
       </c>
       <c r="R34" t="n">
-        <v>6961085.168551165</v>
+        <v>6960820</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4627,7 +4176,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4637,7 +4186,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4673,15 +4222,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>104000132</v>
+        <v>104000059</v>
       </c>
       <c r="B35" t="n">
-        <v>5426</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4689,39 +4233,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>101410</v>
+        <v>4362</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>544999.7260597323</v>
+        <v>544563</v>
       </c>
       <c r="R35" t="n">
-        <v>6960953.762945225</v>
+        <v>6961548</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4753,7 +4292,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4763,7 +4302,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4799,15 +4338,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>104000106</v>
+        <v>104000076</v>
       </c>
       <c r="B36" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4839,10 +4373,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>545005.0042209433</v>
+        <v>545010</v>
       </c>
       <c r="R36" t="n">
-        <v>6961037.173591104</v>
+        <v>6961039</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4874,7 +4408,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4884,7 +4418,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4920,15 +4454,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>104000112</v>
+        <v>104000092</v>
       </c>
       <c r="B37" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4936,21 +4465,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4960,10 +4489,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>544582.3369036738</v>
+        <v>544973</v>
       </c>
       <c r="R37" t="n">
-        <v>6961502.557780011</v>
+        <v>6960989</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4995,7 +4524,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5005,7 +4534,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5041,50 +4570,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>104000165</v>
+        <v>104000099</v>
       </c>
       <c r="B38" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Småmyrorna, Jmt</t>
+          <t>Storflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>544637.5639221109</v>
+        <v>545246</v>
       </c>
       <c r="R38" t="n">
-        <v>6961149.384568993</v>
+        <v>6960730</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5116,7 +4640,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5126,7 +4650,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5162,15 +4686,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>104000176</v>
+        <v>104000106</v>
       </c>
       <c r="B39" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5178,21 +4697,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5202,10 +4721,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544878.0630177166</v>
+        <v>545005</v>
       </c>
       <c r="R39" t="n">
-        <v>6960964.463800776</v>
+        <v>6961037</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5237,7 +4756,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5247,7 +4766,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5283,53 +4802,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119625395</v>
+        <v>104000110</v>
       </c>
       <c r="B40" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>544660</v>
+        <v>544475</v>
       </c>
       <c r="R40" t="n">
-        <v>6961435</v>
+        <v>6961569</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5353,12 +4867,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5369,69 +4893,73 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119625575</v>
+        <v>104000113</v>
       </c>
       <c r="B41" t="n">
-        <v>89252</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Småmyrorna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>545016</v>
+        <v>544932</v>
       </c>
       <c r="R41" t="n">
-        <v>6960898</v>
+        <v>6960572</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5455,12 +4983,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5471,31 +5009,35 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119625574</v>
+        <v>104000162</v>
       </c>
       <c r="B42" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5523,17 +5065,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Storflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544964</v>
+        <v>545200</v>
       </c>
       <c r="R42" t="n">
-        <v>6960939</v>
+        <v>6960831</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5557,12 +5099,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5573,31 +5125,35 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119625597</v>
+        <v>104000185</v>
       </c>
       <c r="B43" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5605,37 +5161,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>545109</v>
+        <v>544629</v>
       </c>
       <c r="R43" t="n">
-        <v>6961124</v>
+        <v>6961516</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5659,12 +5215,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5675,31 +5241,35 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119625380</v>
+        <v>104000188</v>
       </c>
       <c r="B44" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5707,37 +5277,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544678</v>
+        <v>544831</v>
       </c>
       <c r="R44" t="n">
-        <v>6961634</v>
+        <v>6961263</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5761,12 +5331,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5777,31 +5357,35 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119625599</v>
+        <v>104000201</v>
       </c>
       <c r="B45" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5829,17 +5413,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>545111</v>
+        <v>544655</v>
       </c>
       <c r="R45" t="n">
-        <v>6961107</v>
+        <v>6961328</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5863,12 +5447,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5879,31 +5473,35 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119625612</v>
+        <v>119625385</v>
       </c>
       <c r="B46" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5911,21 +5509,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5935,10 +5533,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>544836</v>
+        <v>544570</v>
       </c>
       <c r="R46" t="n">
-        <v>6961292</v>
+        <v>6961546</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5997,37 +5595,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119625382</v>
+        <v>119625392</v>
       </c>
       <c r="B47" t="n">
-        <v>90807</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>65</v>
+        <v>4362</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6037,10 +5630,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544614</v>
+        <v>544655</v>
       </c>
       <c r="R47" t="n">
-        <v>6961561</v>
+        <v>6961452</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6099,37 +5692,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119625383</v>
+        <v>119625396</v>
       </c>
       <c r="B48" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6139,10 +5727,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>544594</v>
+        <v>544660</v>
       </c>
       <c r="R48" t="n">
-        <v>6961545</v>
+        <v>6961435</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6201,15 +5789,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119625585</v>
+        <v>119625574</v>
       </c>
       <c r="B49" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6241,10 +5824,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>545189</v>
+        <v>544964</v>
       </c>
       <c r="R49" t="n">
-        <v>6961131</v>
+        <v>6960939</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6303,37 +5886,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119625391</v>
+        <v>119625576</v>
       </c>
       <c r="B50" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6343,10 +5921,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>544660</v>
+        <v>545048</v>
       </c>
       <c r="R50" t="n">
-        <v>6961476</v>
+        <v>6960895</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6405,37 +5983,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119625606</v>
+        <v>119625578</v>
       </c>
       <c r="B51" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6445,10 +6018,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>544967</v>
+        <v>545085</v>
       </c>
       <c r="R51" t="n">
-        <v>6961196</v>
+        <v>6960933</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6489,7 +6062,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6508,15 +6080,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119625377</v>
+        <v>119625579</v>
       </c>
       <c r="B52" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6524,21 +6091,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6548,10 +6115,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>544634</v>
+        <v>545270</v>
       </c>
       <c r="R52" t="n">
-        <v>6961537</v>
+        <v>6960997</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6610,37 +6177,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119625390</v>
+        <v>119625580</v>
       </c>
       <c r="B53" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6650,10 +6212,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>544640</v>
+        <v>545279</v>
       </c>
       <c r="R53" t="n">
-        <v>6961471</v>
+        <v>6961027</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6712,15 +6274,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119625386</v>
+        <v>119625582</v>
       </c>
       <c r="B54" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6728,21 +6285,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6752,10 +6309,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>544563</v>
+        <v>545184</v>
       </c>
       <c r="R54" t="n">
-        <v>6961544</v>
+        <v>6961041</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6814,15 +6371,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119625393</v>
+        <v>119625585</v>
       </c>
       <c r="B55" t="n">
-        <v>89633</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6830,21 +6382,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6854,10 +6406,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>544660</v>
+        <v>545189</v>
       </c>
       <c r="R55" t="n">
-        <v>6961435</v>
+        <v>6961131</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6916,37 +6468,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119625374</v>
+        <v>119625591</v>
       </c>
       <c r="B56" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6956,10 +6503,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>544655</v>
+        <v>545162</v>
       </c>
       <c r="R56" t="n">
-        <v>6961490</v>
+        <v>6961129</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7000,6 +6547,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7018,37 +6566,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119625607</v>
+        <v>119625594</v>
       </c>
       <c r="B57" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7058,10 +6601,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>544911</v>
+        <v>545146</v>
       </c>
       <c r="R57" t="n">
-        <v>6961201</v>
+        <v>6961121</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7120,15 +6663,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119625591</v>
+        <v>119625596</v>
       </c>
       <c r="B58" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7160,10 +6698,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>545162</v>
+        <v>545102</v>
       </c>
       <c r="R58" t="n">
-        <v>6961129</v>
+        <v>6961133</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7204,7 +6742,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7223,15 +6760,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119625594</v>
+        <v>119625598</v>
       </c>
       <c r="B59" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7263,10 +6795,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>545146</v>
+        <v>545110</v>
       </c>
       <c r="R59" t="n">
-        <v>6961121</v>
+        <v>6961114</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7325,15 +6857,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119625603</v>
+        <v>119625599</v>
       </c>
       <c r="B60" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7341,21 +6868,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7365,10 +6892,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>544968</v>
+        <v>545111</v>
       </c>
       <c r="R60" t="n">
-        <v>6961151</v>
+        <v>6961107</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7427,15 +6954,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119625392</v>
+        <v>104000107</v>
       </c>
       <c r="B61" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7443,37 +6965,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>544655</v>
+        <v>544826</v>
       </c>
       <c r="R61" t="n">
-        <v>6961452</v>
+        <v>6961238</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7497,12 +7019,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7513,35 +7045,39 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119625381</v>
+        <v>104000157</v>
       </c>
       <c r="B62" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -7565,17 +7101,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>544635</v>
+        <v>544574</v>
       </c>
       <c r="R62" t="n">
-        <v>6961580</v>
+        <v>6961535</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7599,12 +7135,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7615,35 +7161,39 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119625378</v>
+        <v>104000175</v>
       </c>
       <c r="B63" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -7667,17 +7217,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>544666</v>
+        <v>544695</v>
       </c>
       <c r="R63" t="n">
-        <v>6961642</v>
+        <v>6961469</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7701,12 +7251,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7717,31 +7277,35 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119625592</v>
+        <v>104000186</v>
       </c>
       <c r="B64" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7749,37 +7313,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>545146</v>
+        <v>544913</v>
       </c>
       <c r="R64" t="n">
-        <v>6961121</v>
+        <v>6961202</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7803,12 +7367,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7819,31 +7393,35 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AS64" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119625581</v>
+        <v>104000192</v>
       </c>
       <c r="B65" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7851,37 +7429,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Småmyrorna, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>545208</v>
+        <v>544646</v>
       </c>
       <c r="R65" t="n">
-        <v>6961020</v>
+        <v>6961200</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7905,12 +7483,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7921,31 +7509,35 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AS65" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119625579</v>
+        <v>119625374</v>
       </c>
       <c r="B66" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7953,21 +7545,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7977,10 +7569,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>545270</v>
+        <v>544655</v>
       </c>
       <c r="R66" t="n">
-        <v>6960997</v>
+        <v>6961490</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8039,15 +7631,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119625578</v>
+        <v>119625378</v>
       </c>
       <c r="B67" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8055,21 +7642,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8079,10 +7666,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>545085</v>
+        <v>544666</v>
       </c>
       <c r="R67" t="n">
-        <v>6960933</v>
+        <v>6961642</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8141,54 +7728,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119625601</v>
+        <v>119625381</v>
       </c>
       <c r="B68" t="n">
-        <v>56522</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>545027</v>
+        <v>544635</v>
       </c>
       <c r="R68" t="n">
-        <v>6961112</v>
+        <v>6961580</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8247,15 +7825,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119625388</v>
+        <v>119625391</v>
       </c>
       <c r="B69" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8263,21 +7836,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8287,10 +7860,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>544609</v>
+        <v>544660</v>
       </c>
       <c r="R69" t="n">
-        <v>6961486</v>
+        <v>6961476</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8349,15 +7922,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119625384</v>
+        <v>119625395</v>
       </c>
       <c r="B70" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8365,21 +7933,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4368</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8389,10 +7957,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>544582</v>
+        <v>544660</v>
       </c>
       <c r="R70" t="n">
-        <v>6961543</v>
+        <v>6961435</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8451,15 +8019,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119625576</v>
+        <v>119625606</v>
       </c>
       <c r="B71" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8467,21 +8030,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8491,10 +8054,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>545048</v>
+        <v>544967</v>
       </c>
       <c r="R71" t="n">
-        <v>6960895</v>
+        <v>6961196</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8535,6 +8098,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8553,37 +8117,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119625584</v>
+        <v>119625607</v>
       </c>
       <c r="B72" t="n">
-        <v>89230</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1596</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8593,10 +8152,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>545189</v>
+        <v>544911</v>
       </c>
       <c r="R72" t="n">
-        <v>6961120</v>
+        <v>6961201</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8655,15 +8214,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119625373</v>
+        <v>119625615</v>
       </c>
       <c r="B73" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8671,21 +8225,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8695,10 +8249,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>544694</v>
+        <v>544748</v>
       </c>
       <c r="R73" t="n">
-        <v>6961492</v>
+        <v>6961477</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8757,53 +8311,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119625398</v>
+        <v>104000083</v>
       </c>
       <c r="B74" t="n">
-        <v>78171</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>544657</v>
+        <v>544581</v>
       </c>
       <c r="R74" t="n">
-        <v>6961420</v>
+        <v>6961508</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8827,12 +8376,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8843,31 +8402,35 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119625582</v>
+        <v>104000084</v>
       </c>
       <c r="B75" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8875,37 +8438,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>545184</v>
+        <v>544702</v>
       </c>
       <c r="R75" t="n">
-        <v>6961041</v>
+        <v>6961453</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8929,12 +8492,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8945,31 +8518,35 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119625583</v>
+        <v>104000094</v>
       </c>
       <c r="B76" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8977,37 +8554,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Våtflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>545192</v>
+        <v>544688</v>
       </c>
       <c r="R76" t="n">
-        <v>6961119</v>
+        <v>6961563</v>
       </c>
       <c r="S76" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9031,12 +8608,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9047,31 +8634,35 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119625593</v>
+        <v>104000165</v>
       </c>
       <c r="B77" t="n">
-        <v>91826</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9079,37 +8670,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3100</v>
+        <v>4366</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Småmyrorna, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>545146</v>
+        <v>544638</v>
       </c>
       <c r="R77" t="n">
-        <v>6961121</v>
+        <v>6961149</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9133,12 +8724,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9149,31 +8750,35 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119625596</v>
+        <v>119625383</v>
       </c>
       <c r="B78" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9181,21 +8786,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9205,10 +8810,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>545102</v>
+        <v>544594</v>
       </c>
       <c r="R78" t="n">
-        <v>6961133</v>
+        <v>6961545</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9267,15 +8872,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119625396</v>
+        <v>119625390</v>
       </c>
       <c r="B79" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9283,21 +8883,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9307,10 +8907,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>544660</v>
+        <v>544640</v>
       </c>
       <c r="R79" t="n">
-        <v>6961435</v>
+        <v>6961471</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9369,15 +8969,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119625387</v>
+        <v>119625384</v>
       </c>
       <c r="B80" t="n">
-        <v>77910</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9385,21 +8980,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6437</v>
+        <v>4368</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9409,10 +9004,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>544571</v>
+        <v>544582</v>
       </c>
       <c r="R80" t="n">
-        <v>6961517</v>
+        <v>6961543</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9471,53 +9066,48 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119625580</v>
+        <v>104000098</v>
       </c>
       <c r="B81" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4362</v>
+        <v>4769</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Storflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>545279</v>
+        <v>545437</v>
       </c>
       <c r="R81" t="n">
-        <v>6961027</v>
+        <v>6960643</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9541,12 +9131,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9557,69 +9157,73 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119625385</v>
+        <v>104000173</v>
       </c>
       <c r="B82" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4362</v>
+        <v>4769</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>våtflobäcken, Jmt</t>
+          <t>Storflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>544570</v>
+        <v>545111</v>
       </c>
       <c r="R82" t="n">
-        <v>6961546</v>
+        <v>6960891</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9643,12 +9247,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9659,53 +9273,57 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119625598</v>
+        <v>119625575</v>
       </c>
       <c r="B83" t="n">
-        <v>91834</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9715,10 +9333,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>545110</v>
+        <v>545016</v>
       </c>
       <c r="R83" t="n">
-        <v>6961114</v>
+        <v>6960898</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9777,37 +9395,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119625615</v>
+        <v>119625588</v>
       </c>
       <c r="B84" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9817,10 +9430,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>544748</v>
+        <v>545183</v>
       </c>
       <c r="R84" t="n">
-        <v>6961477</v>
+        <v>6961139</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9876,6 +9489,1355 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>104000122</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Våtflobäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>544854</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6961114</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>104000171</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Våtflobäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>544671</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6961513</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>119625388</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>våtflobäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>544609</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6961486</v>
+      </c>
+      <c r="S87" t="n">
+        <v>25</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>104000159</v>
+      </c>
+      <c r="B88" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Våtflobäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>544576</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6961517</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>119625387</v>
+      </c>
+      <c r="B89" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>våtflobäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>544571</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6961517</v>
+      </c>
+      <c r="S89" t="n">
+        <v>25</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>104000079</v>
+      </c>
+      <c r="B90" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Storflobäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>545426</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6960672</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>104000095</v>
+      </c>
+      <c r="B91" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Våtflobäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>545033</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6961085</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>104000170</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Våtflobäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>544816</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6961283</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>104000139</v>
+      </c>
+      <c r="B93" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Våtflobäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>544676</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6961506</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>119625601</v>
+      </c>
+      <c r="B94" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>våtflobäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>545027</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6961112</v>
+      </c>
+      <c r="S94" t="n">
+        <v>25</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>104000132</v>
+      </c>
+      <c r="B95" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Våtflobäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>545000</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6960954</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>104000078</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Våtflobäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>544893</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6961304</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50503-2023 artfynd.xlsx
+++ b/artfynd/A 50503-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY96"/>
+  <dimension ref="A1:AZ96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625382</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000147</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000166</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625398</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1214,6 +1239,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000056</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,6 +1341,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625393</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1427,6 +1462,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000116</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1543,6 +1583,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000176</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1640,6 +1685,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625373</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1737,6 +1787,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625380</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1834,6 +1889,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625386</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1950,6 +2010,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000154</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2066,6 +2131,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000105</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2182,6 +2252,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000112</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2298,6 +2373,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000141</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2414,6 +2494,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000146</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2530,6 +2615,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000158</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2627,6 +2717,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625377</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2743,6 +2838,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000044</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2859,6 +2959,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000048</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2975,6 +3080,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000059</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3091,6 +3201,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000110</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3207,6 +3322,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000185</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3323,6 +3443,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000188</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3439,6 +3564,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000201</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3536,6 +3666,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625385</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3633,6 +3768,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625392</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3730,6 +3870,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625396</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3846,6 +3991,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000107</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3962,6 +4112,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000157</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4078,6 +4233,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000175</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4194,6 +4354,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000186</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4310,6 +4475,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000192</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4407,6 +4577,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625374</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4504,6 +4679,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625378</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4601,6 +4781,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625381</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4698,6 +4883,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625391</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4795,6 +4985,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625395</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4892,6 +5087,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625607</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4989,6 +5189,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625615</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5105,6 +5310,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000083</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5221,6 +5431,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000084</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5337,6 +5552,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000094</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5453,6 +5673,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000165</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5550,6 +5775,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625383</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5647,6 +5877,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625390</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5744,6 +5979,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625384</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5865,6 +6105,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000122</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5981,6 +6226,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000171</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6078,6 +6328,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625388</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6194,6 +6449,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000159</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6291,6 +6551,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625387</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6407,6 +6672,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000170</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6523,6 +6793,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000139</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6639,6 +6914,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000078</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6740,6 +7020,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369903</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6856,6 +7141,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000103</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6972,6 +7262,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000128</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7088,6 +7383,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000047</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7185,6 +7485,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625584</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7282,6 +7587,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625583</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7379,6 +7689,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625589</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7476,6 +7791,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625597</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7573,6 +7893,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625593</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7689,6 +8014,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000042</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7786,6 +8116,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625581</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7883,6 +8218,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625592</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7999,6 +8339,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000050</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8115,6 +8460,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000076</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8231,6 +8581,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000092</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8347,6 +8702,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000099</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8463,6 +8823,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000106</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8579,6 +8944,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000113</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8695,6 +9065,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000162</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8792,6 +9167,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625574</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8889,6 +9269,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625576</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8986,6 +9371,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625578</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9083,6 +9473,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625579</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9180,6 +9575,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625580</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9277,6 +9677,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625582</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9374,6 +9779,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625585</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9472,6 +9882,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625591</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9569,6 +9984,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625594</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9666,6 +10086,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625596</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9763,6 +10188,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625598</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9860,6 +10290,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625599</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9958,6 +10393,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625606</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10074,6 +10514,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000098</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10190,6 +10635,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000173</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10287,6 +10737,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625575</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10384,6 +10839,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625588</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10500,6 +10960,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000079</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10616,6 +11081,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000095</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10717,6 +11187,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625601</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10838,8 +11313,110 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000132</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>